--- a/AtchisonRegime/Outputs/Aust/ASX300_Utilities/df_regSummary_ASX300_Utilities.xlsx
+++ b/AtchisonRegime/Outputs/Aust/ASX300_Utilities/df_regSummary_ASX300_Utilities.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7295896495725761</v>
+        <v>0.7370605764745146</v>
       </c>
       <c r="H2" t="n">
-        <v>3.659178140343884</v>
+        <v>3.642524011205614</v>
       </c>
       <c r="I2" t="n">
         <v>-8.016951710911901</v>
@@ -545,16 +545,16 @@
         <v>9.074501372422739</v>
       </c>
       <c r="K2" t="n">
-        <v>35</v>
+        <v>35.21594684385382</v>
       </c>
       <c r="L2" t="n">
         <v>12</v>
       </c>
       <c r="M2" t="n">
-        <v>8.75</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0697568214383283</v>
+        <v>0.0713024323974092</v>
       </c>
       <c r="O2" t="n">
         <v>-0.184079252512853</v>
@@ -603,7 +603,7 @@
         <v>8.09206131391011</v>
       </c>
       <c r="K3" t="n">
-        <v>14.33333333333333</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="L3" t="n">
         <v>12</v>
@@ -661,7 +661,7 @@
         <v>6.97269921720136</v>
       </c>
       <c r="K4" t="n">
-        <v>19.66666666666666</v>
+        <v>19.60132890365449</v>
       </c>
       <c r="L4" t="n">
         <v>10</v>
@@ -719,7 +719,7 @@
         <v>20.8483922702477</v>
       </c>
       <c r="K5" t="n">
-        <v>31</v>
+        <v>30.89700996677741</v>
       </c>
       <c r="L5" t="n">
         <v>12</v>
